--- a/sheets/S08A22P231.xlsx
+++ b/sheets/S08A22P231.xlsx
@@ -26257,7 +26257,7 @@
         <v>13</v>
       </c>
       <c r="G802" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H802" t="s">
         <v>15</v>
@@ -26283,7 +26283,7 @@
         <v>13</v>
       </c>
       <c r="G803" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H803" t="s">
         <v>15</v>
@@ -26309,7 +26309,7 @@
         <v>13</v>
       </c>
       <c r="G804" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H804" t="s">
         <v>15</v>
@@ -26335,7 +26335,7 @@
         <v>13</v>
       </c>
       <c r="G805" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H805" t="s">
         <v>15</v>
@@ -26361,7 +26361,7 @@
         <v>13</v>
       </c>
       <c r="G806" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H806" t="s">
         <v>15</v>
@@ -26387,7 +26387,7 @@
         <v>13</v>
       </c>
       <c r="G807" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H807" t="s">
         <v>15</v>
